--- a/templates/wb_template.xlsx
+++ b/templates/wb_template.xlsx
@@ -7,8 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Шаблон" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Пояснение" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Товары" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,10 +28,6 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="14"/>
     </font>
   </fonts>
   <fills count="3">
@@ -58,7 +53,7 @@
     </border>
     <border>
       <bottom style="thin">
-        <color rgb="00D9E1F2"/>
+        <color rgb="00D9E2F3"/>
       </bottom>
     </border>
   </borders>
@@ -68,9 +63,9 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -436,17 +431,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -477,17 +474,27 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Вес, кг</t>
+          <t>Вес, кг (опц.)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Себестоимость, ₽</t>
+          <t>Себестоимость, ₽ (опц.)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Цена продавца до СПП, ₽</t>
+          <t>Цена продавца до СПП, ₽ (опц.)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Модель продаж (опц.: FBS/FBW)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Дней хранения FBW/FBO (опц.)</t>
         </is>
       </c>
     </row>
@@ -499,27 +506,33 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Горный велосипед 29 дюймов алюминиевый</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
+          <t>Горный велосипед 27.5 алюминиевая рама</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
         <v>140</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="F2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="G2" t="n">
-        <v>18000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>32990</v>
-      </c>
+      <c r="F2" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>12000</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>24990</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>FBS</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -532,69 +545,64 @@
           <t>Дрель-шуруповерт аккумуляторная 18В</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>3200</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>6990</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>FBW</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="n">
         <v>30</v>
-      </c>
-      <c r="D3" t="n">
-        <v>9</v>
-      </c>
-      <c r="E3" t="n">
-        <v>24</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="G3" t="n">
-        <v>3200</v>
-      </c>
-      <c r="H3" t="n">
-        <v>6990</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="110" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Обязательные поля</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Артикул, Наименование, Длина, Ширина, Высота.</t>
-        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Вес, Себестоимость и Цена продавца — необязательные, но сильно улучшают точность экономики.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Если этих колонок нет, проект возьмет значения из config.json.</t>
-        </is>
-      </c>
+          <t>SKU-003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Велосипедный замок цепной 120 см</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>350</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>1190</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
